--- a/测试集/泛用性验收_v3/D40/D40_列换序引用.xlsx
+++ b/测试集/泛用性验收_v3/D40/D40_列换序引用.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选后" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="删除B列后" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D列移入SUM" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,6 +28,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -72,7 +74,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +468,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>SUM</t>
         </is>
       </c>
     </row>
@@ -482,7 +486,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <f>A2+C2</f>
+        <f>SUM(A2:C2)</f>
         <v/>
       </c>
     </row>
@@ -500,7 +504,7 @@
         <v>1000</v>
       </c>
       <c r="E3">
-        <f>A3+C3</f>
+        <f>SUM(A3:C3)</f>
         <v/>
       </c>
     </row>
@@ -518,7 +522,7 @@
         <v>2000</v>
       </c>
       <c r="E4">
-        <f>A4+C4</f>
+        <f>SUM(A4:C4)</f>
         <v/>
       </c>
     </row>
@@ -536,7 +540,7 @@
         <v>3000</v>
       </c>
       <c r="E5">
-        <f>A5+C5</f>
+        <f>SUM(A5:C5)</f>
         <v/>
       </c>
     </row>
@@ -554,7 +558,7 @@
         <v>4000</v>
       </c>
       <c r="E6">
-        <f>A6+C6</f>
+        <f>SUM(A6:C6)</f>
         <v/>
       </c>
     </row>
@@ -590,7 +594,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>SUM</t>
         </is>
       </c>
     </row>
@@ -666,6 +670,137 @@
       </c>
       <c r="D6">
         <f>A6+B6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A值</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>B值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>D值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>SUM(A2:D2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <f>SUM(A3:D3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E4">
+        <f>SUM(A4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <f>SUM(A5:D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" t="n">
+        <v>400</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E6">
+        <f>SUM(A6:D6)</f>
         <v/>
       </c>
     </row>

--- a/测试集/泛用性验收_v3/D40/D40_列换序引用.xlsx
+++ b/测试集/泛用性验收_v3/D40/D40_列换序引用.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="删除B列后" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D列移入SUM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="换列后" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,9 +73,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,22 +465,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUM(A:C)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E2">
         <f>SUM(A2:C2)</f>
@@ -510,16 +507,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E4">
         <f>SUM(A4:C4)</f>
@@ -528,16 +525,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E5">
         <f>SUM(A5:C5)</f>
@@ -546,16 +543,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="E6">
         <f>SUM(A6:C6)</f>
@@ -573,117 +570,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>A值</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>C值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>D值</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>A2+B2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D3">
-        <f>A3+B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D4">
-        <f>A4+B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>300</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D5">
-        <f>A5+B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>400</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D6">
-        <f>A6+B6</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -695,40 +581,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>D值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>B值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>C值</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>D值</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>原SUM内容</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <f>SUM(A2:D2)</f>
+        <f>A2+D2+C2</f>
         <v/>
       </c>
     </row>
@@ -737,70 +623,70 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <f>SUM(A3:D3)</f>
+        <f>A3+D3+C3</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <f>SUM(A4:D4)</f>
+        <f>A4+D4+C4</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <f>SUM(A5:D5)</f>
+        <f>A5+D5+C5</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <f>SUM(A6:D6)</f>
+        <f>A6+D6+C6</f>
         <v/>
       </c>
     </row>
